--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92545357869</v>
+        <v>46157.93121035381</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121035381</v>
+        <v>46157.93372223684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93372223684</v>
+        <v>46157.93678784525</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93678784525</v>
+        <v>46158.28198193262</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28198193262</v>
+        <v>46158.29724326891</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29724326891</v>
+        <v>46158.29795109967</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29795109967</v>
+        <v>46158.33359619541</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33359619541</v>
+        <v>46158.37213093677</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37213093677</v>
+        <v>46158.37269815167</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
